--- a/artfynd/A 40097-2023 artfynd.xlsx
+++ b/artfynd/A 40097-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40097-2023 artfynd.xlsx
+++ b/artfynd/A 40097-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111780504</v>
+        <v>111780464</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507749</v>
+        <v>507793</v>
       </c>
       <c r="R2" t="n">
-        <v>6946170</v>
+        <v>6945996</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111780481</v>
+        <v>111780474</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507726</v>
+        <v>507776</v>
       </c>
       <c r="R3" t="n">
-        <v>6946091</v>
+        <v>6946069</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +882,7 @@
         <v>111780477</v>
       </c>
       <c r="B4" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -936,7 +921,7 @@
         <v>507742</v>
       </c>
       <c r="R4" t="n">
-        <v>6946067</v>
+        <v>6946066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111780494</v>
+        <v>111780481</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507732</v>
+        <v>507726</v>
       </c>
       <c r="R5" t="n">
-        <v>6946115</v>
+        <v>6946090</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111780464</v>
+        <v>111780486</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507793</v>
+        <v>507725</v>
       </c>
       <c r="R6" t="n">
-        <v>6945996</v>
+        <v>6946108</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111780474</v>
+        <v>111780494</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507776</v>
+        <v>507731</v>
       </c>
       <c r="R7" t="n">
-        <v>6946069</v>
+        <v>6946115</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111780486</v>
+        <v>111780504</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507726</v>
+        <v>507749</v>
       </c>
       <c r="R8" t="n">
-        <v>6946108</v>
+        <v>6946169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 40097-2023 artfynd.xlsx
+++ b/artfynd/A 40097-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780464</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780477</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780481</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780486</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780494</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,8 +1421,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111780504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>